--- a/output/Data and Chart Outputs/poland_power_capacity_quarterly.xlsx
+++ b/output/Data and Chart Outputs/poland_power_capacity_quarterly.xlsx
@@ -11,8 +11,9 @@
     <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Chart - Net additions" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Quarterly" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Check_ENTSOE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Releases" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Check_Ember" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Check_ENTSOE" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Releases" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2037,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2058,7 +2059,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ENTSOE_A68_MW</t>
+          <t>Ember_year_end_MW</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -2074,29 +2075,29 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>44197</v>
+        <v>43831</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hydro_MW</t>
+          <t>Solar_MW</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>976</v>
+        <v>477.7</v>
       </c>
       <c r="D2" t="n">
-        <v>604</v>
+        <v>1430</v>
       </c>
       <c r="E2" t="n">
-        <v>372</v>
+        <v>-952.3</v>
       </c>
       <c r="F2" t="n">
-        <v>61.6</v>
+        <v>-66.59999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>44197</v>
+        <v>43831</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -2104,38 +2105,38 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6347.1</v>
+        <v>5917.2</v>
       </c>
       <c r="D3" t="n">
-        <v>6570</v>
+        <v>5840</v>
       </c>
       <c r="E3" t="n">
-        <v>-222.9</v>
+        <v>77.2</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>44197</v>
+        <v>43831</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Solar_MW</t>
+          <t>Hydro_MW</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>887.4</v>
+        <v>973.1</v>
       </c>
       <c r="D4" t="n">
-        <v>3473</v>
+        <v>970</v>
       </c>
       <c r="E4" t="n">
-        <v>-2585.6</v>
+        <v>3.1</v>
       </c>
       <c r="F4" t="n">
-        <v>-74.40000000000001</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5">
@@ -2144,64 +2145,64 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bioenergy_MW</t>
+          <t>Solar_MW</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1598.8</v>
+        <v>887.4</v>
       </c>
       <c r="D5" t="n">
-        <v>880</v>
+        <v>3660</v>
       </c>
       <c r="E5" t="n">
-        <v>718.8</v>
+        <v>-2772.6</v>
       </c>
       <c r="F5" t="n">
-        <v>81.7</v>
+        <v>-75.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>44562</v>
+        <v>44197</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hydro_MW</t>
+          <t>Wind_MW</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>990.5</v>
+        <v>6347.1</v>
       </c>
       <c r="D6" t="n">
-        <v>785</v>
+        <v>6300</v>
       </c>
       <c r="E6" t="n">
-        <v>205.5</v>
+        <v>47.1</v>
       </c>
       <c r="F6" t="n">
-        <v>26.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>44562</v>
+        <v>44197</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wind_MW</t>
+          <t>Hydro_MW</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7159</v>
+        <v>976</v>
       </c>
       <c r="D7" t="n">
-        <v>7950</v>
+        <v>980</v>
       </c>
       <c r="E7" t="n">
-        <v>-791</v>
+        <v>-4</v>
       </c>
       <c r="F7" t="n">
-        <v>-9.9</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="8">
@@ -2217,13 +2218,13 @@
         <v>1693.2</v>
       </c>
       <c r="D8" t="n">
-        <v>6664</v>
+        <v>7090</v>
       </c>
       <c r="E8" t="n">
-        <v>-4970.8</v>
+        <v>-5396.8</v>
       </c>
       <c r="F8" t="n">
-        <v>-74.59999999999999</v>
+        <v>-76.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2232,25 +2233,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bioenergy_MW</t>
+          <t>Wind_MW</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1506.3</v>
+        <v>7159</v>
       </c>
       <c r="D9" t="n">
-        <v>647</v>
+        <v>6970</v>
       </c>
       <c r="E9" t="n">
-        <v>859.3</v>
+        <v>189</v>
       </c>
       <c r="F9" t="n">
-        <v>132.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>44927</v>
+        <v>44562</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2258,16 +2259,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>980.9</v>
+        <v>990.5</v>
       </c>
       <c r="D10" t="n">
-        <v>792</v>
+        <v>970</v>
       </c>
       <c r="E10" t="n">
-        <v>188.9</v>
+        <v>20.5</v>
       </c>
       <c r="F10" t="n">
-        <v>23.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="11">
@@ -2276,20 +2277,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wind_MW</t>
+          <t>Solar_MW</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8287.700000000001</v>
+        <v>3137.4</v>
       </c>
       <c r="D11" t="n">
-        <v>8978</v>
+        <v>11060</v>
       </c>
       <c r="E11" t="n">
-        <v>-690.3</v>
+        <v>-7922.6</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.7</v>
+        <v>-71.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2298,20 +2299,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Solar_MW</t>
+          <t>Wind_MW</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3137.4</v>
+        <v>8287.700000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>10643</v>
+        <v>8150</v>
       </c>
       <c r="E12" t="n">
-        <v>-7505.6</v>
+        <v>137.7</v>
       </c>
       <c r="F12" t="n">
-        <v>-70.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="13">
@@ -2320,20 +2321,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bioenergy_MW</t>
+          <t>Hydro_MW</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1582.7</v>
+        <v>980.9</v>
       </c>
       <c r="D13" t="n">
-        <v>664</v>
+        <v>980</v>
       </c>
       <c r="E13" t="n">
-        <v>918.7</v>
+        <v>0.9</v>
       </c>
       <c r="F13" t="n">
-        <v>138.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
@@ -2342,20 +2343,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hydro_MW</t>
+          <t>Solar_MW</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>982.1</v>
+        <v>5179.8</v>
       </c>
       <c r="D14" t="n">
-        <v>788</v>
+        <v>15920</v>
       </c>
       <c r="E14" t="n">
-        <v>194.1</v>
+        <v>-10740.2</v>
       </c>
       <c r="F14" t="n">
-        <v>24.6</v>
+        <v>-67.5</v>
       </c>
     </row>
     <row r="15">
@@ -2371,13 +2372,13 @@
         <v>9560.5</v>
       </c>
       <c r="D15" t="n">
-        <v>9583</v>
+        <v>9340</v>
       </c>
       <c r="E15" t="n">
-        <v>-22.5</v>
+        <v>220.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -2386,42 +2387,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Solar_MW</t>
+          <t>Hydro_MW</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5179.8</v>
+        <v>982.1</v>
       </c>
       <c r="D16" t="n">
-        <v>14609</v>
+        <v>990</v>
       </c>
       <c r="E16" t="n">
-        <v>-9429.200000000001</v>
+        <v>-7.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-64.5</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>45292</v>
+        <v>45658</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bioenergy_MW</t>
+          <t>Solar_MW</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1545.3</v>
+        <v>8556.4</v>
       </c>
       <c r="D17" t="n">
-        <v>662</v>
+        <v>21720</v>
       </c>
       <c r="E17" t="n">
-        <v>883.3</v>
+        <v>-13163.6</v>
       </c>
       <c r="F17" t="n">
-        <v>133.4</v>
+        <v>-60.6</v>
       </c>
     </row>
     <row r="18">
@@ -2430,20 +2431,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hydro_MW</t>
+          <t>Wind_MW</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>984.6</v>
+        <v>10522.4</v>
       </c>
       <c r="D18" t="n">
-        <v>790</v>
+        <v>10150</v>
       </c>
       <c r="E18" t="n">
-        <v>194.6</v>
+        <v>372.4</v>
       </c>
       <c r="F18" t="n">
-        <v>24.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="19">
@@ -2452,25 +2453,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wind_MW</t>
+          <t>Hydro_MW</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10522.4</v>
+        <v>984.6</v>
       </c>
       <c r="D19" t="n">
-        <v>10299</v>
+        <v>990</v>
       </c>
       <c r="E19" t="n">
-        <v>223.4</v>
+        <v>-5.4</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>45658</v>
+        <v>46023</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2478,38 +2479,38 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8556.4</v>
+        <v>11572.4</v>
       </c>
       <c r="D20" t="n">
-        <v>17816</v>
+        <v>25420</v>
       </c>
       <c r="E20" t="n">
-        <v>-9259.6</v>
+        <v>-13847.6</v>
       </c>
       <c r="F20" t="n">
-        <v>-52</v>
+        <v>-54.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>45658</v>
+        <v>46023</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bioenergy_MW</t>
+          <t>Wind_MW</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1576.4</v>
+        <v>10975.7</v>
       </c>
       <c r="D21" t="n">
-        <v>636</v>
+        <v>10600</v>
       </c>
       <c r="E21" t="n">
-        <v>940.4</v>
+        <v>375.7</v>
       </c>
       <c r="F21" t="n">
-        <v>147.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="22">
@@ -2525,79 +2526,13 @@
         <v>985.5</v>
       </c>
       <c r="D22" t="n">
-        <v>791</v>
+        <v>990</v>
       </c>
       <c r="E22" t="n">
-        <v>194.5</v>
+        <v>-4.5</v>
       </c>
       <c r="F22" t="n">
-        <v>24.6</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Wind_MW</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>10975.7</v>
-      </c>
-      <c r="D23" t="n">
-        <v>10700</v>
-      </c>
-      <c r="E23" t="n">
-        <v>275.7</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Solar_MW</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>11572.4</v>
-      </c>
-      <c r="D24" t="n">
-        <v>20734</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-9161.6</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-44.2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Bioenergy_MW</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1515.9</v>
-      </c>
-      <c r="D25" t="n">
-        <v>698</v>
-      </c>
-      <c r="E25" t="n">
-        <v>817.9</v>
-      </c>
-      <c r="F25" t="n">
-        <v>117.2</v>
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -2611,6 +2546,580 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>this_file_MW</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ENTSOE_A68_MW</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>difference_MW</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difference_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Hydro_MW</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>976</v>
+      </c>
+      <c r="D2" t="n">
+        <v>604</v>
+      </c>
+      <c r="E2" t="n">
+        <v>372</v>
+      </c>
+      <c r="F2" t="n">
+        <v>61.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6347.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6570</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-222.9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>887.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3473</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-2585.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-74.40000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bioenergy_MW</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1598.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>880</v>
+      </c>
+      <c r="E5" t="n">
+        <v>718.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>81.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hydro_MW</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>990.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>785</v>
+      </c>
+      <c r="E6" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>7159</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7950</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-791</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-9.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1693.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6664</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-4970.8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-74.59999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bioenergy_MW</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1506.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>647</v>
+      </c>
+      <c r="E9" t="n">
+        <v>859.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>132.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hydro_MW</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>980.9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>792</v>
+      </c>
+      <c r="E10" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>8287.700000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8978</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-690.3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3137.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10643</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-7505.6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-70.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bioenergy_MW</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1582.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>664</v>
+      </c>
+      <c r="E13" t="n">
+        <v>918.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>138.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hydro_MW</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>982.1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>788</v>
+      </c>
+      <c r="E14" t="n">
+        <v>194.1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>9560.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9583</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5179.8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>14609</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-9429.200000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-64.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bioenergy_MW</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1545.3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>662</v>
+      </c>
+      <c r="E17" t="n">
+        <v>883.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>133.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hydro_MW</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>984.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>790</v>
+      </c>
+      <c r="E18" t="n">
+        <v>194.6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10522.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10299</v>
+      </c>
+      <c r="E19" t="n">
+        <v>223.4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>8556.4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>17816</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-9259.6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-52</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bioenergy_MW</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1576.4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>636</v>
+      </c>
+      <c r="E21" t="n">
+        <v>940.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>147.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Hydro_MW</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>985.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>791</v>
+      </c>
+      <c r="E22" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10975.7</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10700</v>
+      </c>
+      <c r="E23" t="n">
+        <v>275.7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>11572.4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>20734</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-9161.6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-44.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bioenergy_MW</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1515.9</v>
+      </c>
+      <c r="D25" t="n">
+        <v>698</v>
+      </c>
+      <c r="E25" t="n">
+        <v>817.9</v>
+      </c>
+      <c r="F25" t="n">
+        <v>117.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2644,7 +3153,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2666,7 +3175,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2688,7 +3197,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2710,7 +3219,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2732,7 +3241,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2754,7 +3263,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2776,7 +3285,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2798,7 +3307,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2820,7 +3329,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2842,7 +3351,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2864,7 +3373,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2886,7 +3395,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2908,7 +3417,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2930,7 +3439,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2952,7 +3461,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/output/Data and Chart Outputs/poland_power_capacity_quarterly.xlsx
+++ b/output/Data and Chart Outputs/poland_power_capacity_quarterly.xlsx
@@ -3153,7 +3153,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/output/Data and Chart Outputs/poland_power_capacity_quarterly.xlsx
+++ b/output/Data and Chart Outputs/poland_power_capacity_quarterly.xlsx
@@ -1071,7 +1071,7 @@
         <v>1.138</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6006</v>
+        <v>1.6007</v>
       </c>
       <c r="F3" t="n">
         <v>0.1698</v>
@@ -1091,7 +1091,7 @@
         <v>1.6932</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5063</v>
+        <v>1.5062</v>
       </c>
       <c r="F4" t="n">
         <v>0.1698</v>
@@ -1151,7 +1151,7 @@
         <v>5.1798</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5453</v>
+        <v>1.5454</v>
       </c>
       <c r="F7" t="n">
         <v>0.1715</v>
@@ -1171,7 +1171,7 @@
         <v>6.6207</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5532</v>
+        <v>1.5533</v>
       </c>
       <c r="F8" t="n">
         <v>0.1725</v>
@@ -1191,7 +1191,7 @@
         <v>8.5564</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5764</v>
+        <v>1.5763</v>
       </c>
       <c r="F9" t="n">
         <v>0.1862</v>
@@ -1271,7 +1271,7 @@
         <v>11.5724</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5159</v>
+        <v>1.5158</v>
       </c>
       <c r="F13" t="n">
         <v>0.2342</v>
@@ -1576,10 +1576,10 @@
         <v>477.7</v>
       </c>
       <c r="E2" t="n">
-        <v>1738.2</v>
+        <v>1738.3</v>
       </c>
       <c r="G2" t="n">
-        <v>9106.200000000001</v>
+        <v>9106.299999999999</v>
       </c>
       <c r="H2" t="n">
         <v>245.4</v>
@@ -1611,7 +1611,7 @@
         <v>169.8</v>
       </c>
       <c r="G3" t="n">
-        <v>9979.200000000001</v>
+        <v>9979.1</v>
       </c>
       <c r="H3" t="n">
         <v>255.7</v>
@@ -1634,7 +1634,7 @@
         <v>1138</v>
       </c>
       <c r="E4" t="n">
-        <v>1600.6</v>
+        <v>1600.7</v>
       </c>
       <c r="F4" t="n">
         <v>169.8</v>
@@ -1663,7 +1663,7 @@
         <v>1693.2</v>
       </c>
       <c r="E5" t="n">
-        <v>1506.3</v>
+        <v>1506.2</v>
       </c>
       <c r="F5" t="n">
         <v>169.8</v>
@@ -1698,7 +1698,7 @@
         <v>171.5</v>
       </c>
       <c r="G6" t="n">
-        <v>14160.1</v>
+        <v>14160.2</v>
       </c>
       <c r="H6" t="n">
         <v>275.6</v>
@@ -1753,13 +1753,13 @@
         <v>5179.8</v>
       </c>
       <c r="E8" t="n">
-        <v>1545.3</v>
+        <v>1545.4</v>
       </c>
       <c r="F8" t="n">
         <v>171.5</v>
       </c>
       <c r="G8" t="n">
-        <v>17439.2</v>
+        <v>17439.3</v>
       </c>
       <c r="H8" t="n">
         <v>295.3</v>
@@ -1785,13 +1785,13 @@
         <v>6620.7</v>
       </c>
       <c r="E9" t="n">
-        <v>1553.2</v>
+        <v>1553.3</v>
       </c>
       <c r="F9" t="n">
         <v>172.5</v>
       </c>
       <c r="G9" t="n">
-        <v>19193.8</v>
+        <v>19193.9</v>
       </c>
       <c r="H9" t="n">
         <v>301.2</v>
@@ -1817,13 +1817,13 @@
         <v>8556.4</v>
       </c>
       <c r="E10" t="n">
-        <v>1576.4</v>
+        <v>1576.3</v>
       </c>
       <c r="F10" t="n">
         <v>186.2</v>
       </c>
       <c r="G10" t="n">
-        <v>21826</v>
+        <v>21825.9</v>
       </c>
       <c r="H10" t="n">
         <v>313.3</v>
@@ -1887,7 +1887,7 @@
         <v>204.1</v>
       </c>
       <c r="G12" t="n">
-        <v>23432</v>
+        <v>23431.9</v>
       </c>
       <c r="H12" t="n">
         <v>326.8</v>
@@ -1919,7 +1919,7 @@
         <v>234.2</v>
       </c>
       <c r="G13" t="n">
-        <v>24629.6</v>
+        <v>24629.5</v>
       </c>
       <c r="H13" t="n">
         <v>326.1</v>
@@ -1945,13 +1945,13 @@
         <v>11572.4</v>
       </c>
       <c r="E14" t="n">
-        <v>1515.9</v>
+        <v>1515.8</v>
       </c>
       <c r="F14" t="n">
         <v>234.2</v>
       </c>
       <c r="G14" t="n">
-        <v>25283.7</v>
+        <v>25283.6</v>
       </c>
       <c r="H14" t="n">
         <v>328.4</v>
@@ -2745,13 +2745,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1506.3</v>
+        <v>1506.2</v>
       </c>
       <c r="D9" t="n">
         <v>647</v>
       </c>
       <c r="E9" t="n">
-        <v>859.3</v>
+        <v>859.2</v>
       </c>
       <c r="F9" t="n">
         <v>132.8</v>
@@ -2921,13 +2921,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1545.3</v>
+        <v>1545.4</v>
       </c>
       <c r="D17" t="n">
         <v>662</v>
       </c>
       <c r="E17" t="n">
-        <v>883.3</v>
+        <v>883.4</v>
       </c>
       <c r="F17" t="n">
         <v>133.4</v>
@@ -3009,16 +3009,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1576.4</v>
+        <v>1576.3</v>
       </c>
       <c r="D21" t="n">
         <v>636</v>
       </c>
       <c r="E21" t="n">
-        <v>940.4</v>
+        <v>940.3</v>
       </c>
       <c r="F21" t="n">
-        <v>147.9</v>
+        <v>147.8</v>
       </c>
     </row>
     <row r="22">
@@ -3097,13 +3097,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1515.9</v>
+        <v>1515.8</v>
       </c>
       <c r="D25" t="n">
         <v>698</v>
       </c>
       <c r="E25" t="n">
-        <v>817.9</v>
+        <v>817.8</v>
       </c>
       <c r="F25" t="n">
         <v>117.2</v>
@@ -3148,7 +3148,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 30 czerwca 2026 r.</t>
+          <t>Instalacje OZE - stan na 31 grudnia 2025 r.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3158,19 +3158,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/16383/mapaozena30-06-2026.xlsx; size 587715</t>
+          <t>https://www.ure.gov.pl/download/9/16120/mapaozena31-12-2025nastroneURE.xlsx; size 560189</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0a0c1e9798c880e23146b96e4843494bae02f9265a38ded2b91765d1b1fbaac1</t>
+          <t>2ea7e80a5dec4ea637d3fe7b5ec31f8f763df80614e0275ef73321cbba854007</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 31 marca 2026 r.</t>
+          <t>Instalacje OZE - stan na 30 września 2025 r.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3180,19 +3180,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/16263/mapaozena31-03-2026nastroneURE.xlsx; size 578167</t>
+          <t>https://www.ure.gov.pl/download/9/15842/MapaOZEna30-09-2025nastrURE.xlsx; size 543959</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2dd0e6168e2cd9a4f79021ef48e3bad03e02c70582f542001d7b84d87d6c94a5</t>
+          <t>b40f78f79525647572537168ccb69cc114e5db5b58a50b309962c941f9acc6b8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 31 grudnia 2025 r.</t>
+          <t>Instalacje OZE - stan na 30 czerwca 2025 r.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3202,19 +3202,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/16120/mapaozena31-12-2025nastroneURE.xlsx; size 560189</t>
+          <t>https://www.ure.gov.pl/download/9/15727/Mapana30-06-2025nastroneURE.xlsx; size 523324</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2ea7e80a5dec4ea637d3fe7b5ec31f8f763df80614e0275ef73321cbba854007</t>
+          <t>9630c42ef43f6e50495778247722532940107a09d753099e36c142aafcd3b2ba</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 30 września 2025 r.</t>
+          <t>Instalacje OZE - stan na 31 marca 2025 r.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3224,19 +3224,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/15842/MapaOZEna30-09-2025nastrURE.xlsx; size 543959</t>
+          <t>https://www.ure.gov.pl/download/9/15413/Mapana31-03-2025nastroneUREuaktualnienie.xlsx; size 505634</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>b40f78f79525647572537168ccb69cc114e5db5b58a50b309962c941f9acc6b8</t>
+          <t>a364b28a99fe9afa8f3fbdd6ae0f640cac727845fc3e4b5f8807b9a4ca79604d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 30 czerwca 2025 r.</t>
+          <t>Instalacje OZE - stan na 31 grudnia 2024 r.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3246,19 +3246,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/15727/Mapana30-06-2025nastroneURE.xlsx; size 523324</t>
+          <t>https://www.ure.gov.pl/download/9/15225/MapaOZEnastrURE.xlsx; size 482572</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9630c42ef43f6e50495778247722532940107a09d753099e36c142aafcd3b2ba</t>
+          <t>b468064e75cf6e9af93fbc3d7a2f1b89655a8795d672eb21d21446e6ae8cac49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 31 marca 2025 r.</t>
+          <t>Instalacje OZE - stan na 30 czerwca 2024 r.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3268,19 +3268,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/15413/Mapana31-03-2025nastroneUREuaktualnienie.xlsx; size 505634</t>
+          <t>https://www.ure.gov.pl/download/9/14986/Mapaozenastrinternetowa.xlsx; size 433936</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>a364b28a99fe9afa8f3fbdd6ae0f640cac727845fc3e4b5f8807b9a4ca79604d</t>
+          <t>c7d4ad4cc8894374c68d69a00fccc5742dda804ed54807be04434127aad41bbe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 31 grudnia 2024 r.</t>
+          <t>Instalacje OZE - stan na 31 grudnia 2023 r.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3290,19 +3290,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/15225/MapaOZEnastrURE.xlsx; size 482572</t>
+          <t>https://www.ure.gov.pl/download/9/14587/2023-12-31mapanastroneURE.xlsx; size 399649</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>b468064e75cf6e9af93fbc3d7a2f1b89655a8795d672eb21d21446e6ae8cac49</t>
+          <t>9c655be0dd3cf98d8ffa2d1d0059ff0e56e4c2e54ab8cc9b667c5d1adc2364ce</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 30 czerwca 2024 r.</t>
+          <t>Instalacje OZE - stan na 30 czerwca 2023 r.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3312,19 +3312,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/14986/Mapaozenastrinternetowa.xlsx; size 433936</t>
+          <t>https://www.ure.gov.pl/download/9/13999/MAPAna30-06-2023.xlsx; size 348358</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>c7d4ad4cc8894374c68d69a00fccc5742dda804ed54807be04434127aad41bbe</t>
+          <t>101889596065a1e46e2e56f2d379ad0efbb967ce68a61a7c1448185e5d2e2d41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 31 grudnia 2023 r.</t>
+          <t>Instalacje OZE - stan na 31 grudnia 2022 r.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3334,19 +3334,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/14587/2023-12-31mapanastroneURE.xlsx; size 399649</t>
+          <t>https://www.ure.gov.pl/download/9/13797/MAPAna31-12-2022nastronezprzypisem.xlsx; size 314212</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9c655be0dd3cf98d8ffa2d1d0059ff0e56e4c2e54ab8cc9b667c5d1adc2364ce</t>
+          <t>9626621f45303f8a5fe6f8ae46c818d77e2a0daaba14bd89be7e71a8673c22c5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 30 czerwca 2023 r.</t>
+          <t>Instalacje OZE - stan na 31 grudnia 2021 r.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3356,19 +3356,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/13999/MAPAna30-06-2023.xlsx; size 348358</t>
+          <t>https://www.ure.gov.pl/download/9/12809/file.file; size 184211</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>101889596065a1e46e2e56f2d379ad0efbb967ce68a61a7c1448185e5d2e2d41</t>
+          <t>5f374afd3bcbc2c1c266beaad4ba6ec64e2f3babad6f0ebe6c804796b7eb70f5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 31 grudnia 2022 r.</t>
+          <t>Instalacje OZE - stan na 30 czerwca 2021 r.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3378,19 +3378,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/13797/MAPAna31-12-2022nastronezprzypisem.xlsx; size 314212</t>
+          <t>https://www.ure.gov.pl/download/9/12287/file.file; size 150488</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9626621f45303f8a5fe6f8ae46c818d77e2a0daaba14bd89be7e71a8673c22c5</t>
+          <t>ce55be032684eed7fb2e5c7eb3fd7312f77b2c3e99de54151a541b359012b290</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 31 grudnia 2021 r.</t>
+          <t>Instalacje OZE - stan na 31 grudnia 2020 r.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3400,19 +3400,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/12809/file.file; size 184211</t>
+          <t>https://www.ure.gov.pl/download/9/11882/MapaOZEnastroneURE31-12-2020.xlsx; size 138669</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5f374afd3bcbc2c1c266beaad4ba6ec64e2f3babad6f0ebe6c804796b7eb70f5</t>
+          <t>ac087cc952b0baf3ea1eb27c35d7b73eda68c0e590c72826ee94a33db8ebb4ef</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 30 czerwca 2021 r.</t>
+          <t>Instalacje OZE - stan na 31 grudnia 2019 r.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3422,56 +3422,56 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/12287/file.file; size 150488</t>
+          <t>https://www.ure.gov.pl/download/9/10922/Instalacjeodnawialnychzrodelenergiiwgstanunadzien31grudnia2019r.xlsx; size 117888</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ce55be032684eed7fb2e5c7eb3fd7312f77b2c3e99de54151a541b359012b290</t>
+          <t>76640c245e154ba40808924ba9f76340dfe5e3b002bd908ae0e46921be91af70</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 31 grudnia 2020 r.</t>
+          <t>Instalacje OZE - stan na 30 czerwca 2026 r.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-12 04:21 UTC</t>
+          <t>2026-10-12 04:23 UTC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/11882/MapaOZEnastroneURE31-12-2020.xlsx; size 138669</t>
+          <t>https://www.ure.gov.pl/download/9/16383/mapaozena30-06-2026.xlsx; size 587715</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ac087cc952b0baf3ea1eb27c35d7b73eda68c0e590c72826ee94a33db8ebb4ef</t>
+          <t>0a0c1e9798c880e23146b96e4843494bae02f9265a38ded2b91765d1b1fbaac1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 31 grudnia 2019 r.</t>
+          <t>Instalacje OZE - stan na 31 marca 2026 r.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-12 04:21 UTC</t>
+          <t>2026-10-12 04:23 UTC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/10922/Instalacjeodnawialnychzrodelenergiiwgstanunadzien31grudnia2019r.xlsx; size 117888</t>
+          <t>https://www.ure.gov.pl/download/9/16263/mapaozena31-03-2026nastroneURE.xlsx; size 578167</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>76640c245e154ba40808924ba9f76340dfe5e3b002bd908ae0e46921be91af70</t>
+          <t>2dd0e6168e2cd9a4f79021ef48e3bad03e02c70582f542001d7b84d87d6c94a5</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/poland_power_capacity_quarterly.xlsx
+++ b/output/Data and Chart Outputs/poland_power_capacity_quarterly.xlsx
@@ -160,7 +160,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Poland renewable capacity at quarter end (URE register, partial) (to Jul/26)</a:t>
+              <a:t>Poland renewable capacity at quarter end (URE register, partial) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -190,12 +190,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$15</f>
+              <f>'Chart'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$15</f>
+              <f>'Chart'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -218,12 +218,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$15</f>
+              <f>'Chart'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$15</f>
+              <f>'Chart'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -246,12 +246,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$15</f>
+              <f>'Chart'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$15</f>
+              <f>'Chart'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -274,12 +274,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$15</f>
+              <f>'Chart'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$15</f>
+              <f>'Chart'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -302,12 +302,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$15</f>
+              <f>'Chart'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$15</f>
+              <f>'Chart'!$F$2:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -408,7 +408,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Poland renewable capacity at quarter end (URE register net additions of solar and wind per release (quarter) (to Jul/26)</a:t>
+              <a:t>Poland renewable capacity at quarter end (URE register net additions of solar and wind per release (quarter) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -438,12 +438,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Net additions'!$A$2:$A$14</f>
+              <f>'Chart - Net additions'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Net additions'!$B$2:$B$14</f>
+              <f>'Chart - Net additions'!$B$2:$B$15</f>
             </numRef>
           </val>
         </ser>
@@ -466,12 +466,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Net additions'!$A$2:$A$14</f>
+              <f>'Chart - Net additions'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Net additions'!$C$2:$C$14</f>
+              <f>'Chart - Net additions'!$C$2:$C$15</f>
             </numRef>
           </val>
         </ser>
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1314,6 +1314,26 @@
         <v>1.5321</v>
       </c>
       <c r="F15" t="n">
+        <v>0.2423</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.9911</v>
+      </c>
+      <c r="C16" t="n">
+        <v>11.3062</v>
+      </c>
+      <c r="D16" t="n">
+        <v>13.4402</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.5373</v>
+      </c>
+      <c r="F16" t="n">
         <v>0.2423</v>
       </c>
     </row>
@@ -1329,7 +1349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1493,6 +1513,17 @@
       </c>
       <c r="C14" t="n">
         <v>32.19999999999891</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B15" t="n">
+        <v>678.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-88.59999999999854</v>
       </c>
     </row>
   </sheetData>
@@ -1507,7 +1538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1983,7 +2014,7 @@
         <v>234.2</v>
       </c>
       <c r="G15" t="n">
-        <v>26193.8</v>
+        <v>26193.7</v>
       </c>
       <c r="H15" t="n">
         <v>335.2</v>
@@ -2025,6 +2056,38 @@
       </c>
       <c r="J16" t="n">
         <v>12875.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B17" t="n">
+        <v>991.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>11306.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>13440.2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1537.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>242.3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>27517.1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>341.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1195.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>12740.3</v>
       </c>
     </row>
   </sheetData>
@@ -3120,7 +3183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3434,7 +3497,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 30 czerwca 2026 r.</t>
+          <t>Instalacje OZE - stan na 31 marca 2026 r.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3444,34 +3507,56 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/16383/mapaozena30-06-2026.xlsx; size 587715</t>
+          <t>https://www.ure.gov.pl/download/9/16263/mapaozena31-03-2026nastroneURE.xlsx; size 578167</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0a0c1e9798c880e23146b96e4843494bae02f9265a38ded2b91765d1b1fbaac1</t>
+          <t>2dd0e6168e2cd9a4f79021ef48e3bad03e02c70582f542001d7b84d87d6c94a5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Instalacje OZE - stan na 31 marca 2026 r.</t>
+          <t>Instalacje OZE - stan na 30 września 2026 r.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-12 04:23 UTC</t>
+          <t>2026-10-28 01:17 UTC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.ure.gov.pl/download/9/16263/mapaozena31-03-2026nastroneURE.xlsx; size 578167</t>
+          <t>https://www.ure.gov.pl/download/9/16535/MAPAOZEna30092026nastroneURE.xlsx; size 607802</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2dd0e6168e2cd9a4f79021ef48e3bad03e02c70582f542001d7b84d87d6c94a5</t>
+          <t>8bb08d77f0382f48f677512dc4a88f9a41c55f4f90a998f8f8acfe20632f5692</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Instalacje OZE - stan na 30 czerwca 2026 r.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-28 01:17 UTC</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.ure.gov.pl/download/9/16383/mapaozena30-06-2026.xlsx; size 587715</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0a0c1e9798c880e23146b96e4843494bae02f9265a38ded2b91765d1b1fbaac1</t>
         </is>
       </c>
     </row>
